--- a/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/xd04_output_mapping.xlsx
+++ b/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/xd04_output_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_PWM_Rev_0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C179213-991D-44E2-84DF-80B40223BE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D081EC9-6BA2-4FC2-87EF-DB7996A916A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,24 +35,104 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1, 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2, 4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9, 11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10, 12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>output
 ch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 3</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 11</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 12</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -60,7 +140,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,6 +150,22 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -102,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -114,6 +210,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -413,13 +512,13 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.6">
@@ -427,8 +526,8 @@
       <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
+      <c r="D4" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.6">
@@ -436,8 +535,8 @@
       <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
+      <c r="D5" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.6">
@@ -445,8 +544,8 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/xd04_output_mapping.xlsx
+++ b/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/xd04_output_mapping.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_PWM_Rev_0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D081EC9-6BA2-4FC2-87EF-DB7996A916A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DA2EF2-1435-43AD-9BE6-A5340D8AEE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -206,13 +217,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -511,40 +522,40 @@
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B6" s="4"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
